--- a/data/trans_orig/P2C_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197199</t>
+          <t>199001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249049</t>
+          <t>250692</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>319343</t>
+          <t>316617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>383110</t>
+          <t>382927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>528403</t>
+          <t>530000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>609244</t>
+          <t>614085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>782674</t>
+          <t>781031</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>834524</t>
+          <t>832722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>932003</t>
+          <t>932186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>995770</t>
+          <t>998496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1737591</t>
+          <t>1732750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1818432</t>
+          <t>1816835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>527150</t>
+          <t>527451</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>606385</t>
+          <t>605538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>602168</t>
+          <t>598865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>681407</t>
+          <t>679650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1151134</t>
+          <t>1153496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1262365</t>
+          <t>1258175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1087028</t>
+          <t>1087875</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1166263</t>
+          <t>1165962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>906266</t>
+          <t>908023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>985505</t>
+          <t>988808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2018721</t>
+          <t>2022911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2129952</t>
+          <t>2127590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144712</t>
+          <t>144627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188940</t>
+          <t>188324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159195</t>
+          <t>157496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202074</t>
+          <t>200591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>315354</t>
+          <t>314220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>378215</t>
+          <t>376466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>362468</t>
+          <t>363084</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406696</t>
+          <t>406781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>274338</t>
+          <t>275821</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>317217</t>
+          <t>318916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649605</t>
+          <t>651354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>712466</t>
+          <t>713600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>899229</t>
+          <t>902370</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1010203</t>
+          <t>1007998</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1110807</t>
+          <t>1112673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1218215</t>
+          <t>1224850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2042280</t>
+          <t>2052399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2190236</t>
+          <t>2205057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2266340</t>
+          <t>2268545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2377314</t>
+          <t>2374173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2160982</t>
+          <t>2154347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2268390</t>
+          <t>2266524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4465505</t>
+          <t>4450684</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4613461</t>
+          <t>4603342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>356617</t>
+          <t>354101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>420238</t>
+          <t>416326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>542731</t>
+          <t>540498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>618945</t>
+          <t>615255</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>918087</t>
+          <t>918371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1015536</t>
+          <t>1019677</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>554405</t>
+          <t>558317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>618026</t>
+          <t>620542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>718852</t>
+          <t>722542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>795066</t>
+          <t>797299</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1296904</t>
+          <t>1292763</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1394353</t>
+          <t>1394069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>901167</t>
+          <t>901906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>989244</t>
+          <t>990419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>975761</t>
+          <t>979400</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1060277</t>
+          <t>1065501</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1909315</t>
+          <t>1907119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2030316</t>
+          <t>2035298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>974713</t>
+          <t>973538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1062790</t>
+          <t>1062051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>697526</t>
+          <t>692302</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>782042</t>
+          <t>778403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1691444</t>
+          <t>1686462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1812445</t>
+          <t>1814641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172668</t>
+          <t>173084</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>219146</t>
+          <t>218433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211986</t>
+          <t>213919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>258900</t>
+          <t>257928</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>395531</t>
+          <t>396623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>461576</t>
+          <t>463409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>262035</t>
+          <t>262748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308513</t>
+          <t>308097</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>199731</t>
+          <t>200703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>246645</t>
+          <t>244712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>478237</t>
+          <t>476404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>544282</t>
+          <t>543190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1468580</t>
+          <t>1471706</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1596940</t>
+          <t>1590298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1774871</t>
+          <t>1766895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1894574</t>
+          <t>1889323</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3277086</t>
+          <t>3272612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3444669</t>
+          <t>3446041</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1822842</t>
+          <t>1829484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1951202</t>
+          <t>1948076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1659656</t>
+          <t>1664907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1779359</t>
+          <t>1787335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3529343</t>
+          <t>3527971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3696926</t>
+          <t>3701400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>188811</t>
+          <t>187175</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>236198</t>
+          <t>234468</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>308008</t>
+          <t>306511</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>367595</t>
+          <t>369351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>506726</t>
+          <t>508664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>587853</t>
+          <t>587789</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>518149</t>
+          <t>519879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>565536</t>
+          <t>567172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>627065</t>
+          <t>625309</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686652</t>
+          <t>688149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1161154</t>
+          <t>1161218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1242281</t>
+          <t>1240343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>636539</t>
+          <t>640077</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>721259</t>
+          <t>722617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>764354</t>
+          <t>770649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>853021</t>
+          <t>854981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1433012</t>
+          <t>1424440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1552597</t>
+          <t>1556375</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1355126</t>
+          <t>1353768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1439846</t>
+          <t>1436308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1135279</t>
+          <t>1133319</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1223946</t>
+          <t>1217651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2512088</t>
+          <t>2508310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2631673</t>
+          <t>2640245</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145804</t>
+          <t>148610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191698</t>
+          <t>192795</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201861</t>
+          <t>200332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>246018</t>
+          <t>247330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>362675</t>
+          <t>356025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>426007</t>
+          <t>425595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>355188</t>
+          <t>354091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>401082</t>
+          <t>398276</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303122</t>
+          <t>301810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>347279</t>
+          <t>348808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>670020</t>
+          <t>670432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>733352</t>
+          <t>740002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1004295</t>
+          <t>1000723</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1113235</t>
+          <t>1113981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1311423</t>
+          <t>1311616</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1431695</t>
+          <t>1435478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2352996</t>
+          <t>2346461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2514661</t>
+          <t>2509717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2264383</t>
+          <t>2263637</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2373323</t>
+          <t>2376895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2100405</t>
+          <t>2096622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2220677</t>
+          <t>2220484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4395057</t>
+          <t>4400001</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4556722</t>
+          <t>4563257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,04%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76399</t>
+          <t>75401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107019</t>
+          <t>105832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>180178</t>
+          <t>178755</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>214080</t>
+          <t>215870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>263002</t>
+          <t>265133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>310958</t>
+          <t>312765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407919</t>
+          <t>409106</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438539</t>
+          <t>439537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>541428</t>
+          <t>539638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>575330</t>
+          <t>576753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>959488</t>
+          <t>957681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1007444</t>
+          <t>1005313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183098</t>
+          <t>171996</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>302500</t>
+          <t>299532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>334101</t>
+          <t>338104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>995450</t>
+          <t>948365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>573269</t>
+          <t>568671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1366589</t>
+          <t>1388735</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1987827</t>
+          <t>1990795</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2107229</t>
+          <t>2118331</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1242373</t>
+          <t>1289458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1903722</t>
+          <t>1899719</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3161561</t>
+          <t>3139415</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3954881</t>
+          <t>3959479</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50749</t>
+          <t>51391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86480</t>
+          <t>88319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59984</t>
+          <t>61398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87341</t>
+          <t>87154</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119396</t>
+          <t>119173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164665</t>
+          <t>165568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>560143</t>
+          <t>558304</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>595874</t>
+          <t>595232</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>573122</t>
+          <t>573309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>600479</t>
+          <t>599065</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1142421</t>
+          <t>1141518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1187690</t>
+          <t>1187913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>320520</t>
+          <t>313974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>463371</t>
+          <t>463942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>605770</t>
+          <t>607145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1353599</t>
+          <t>1318773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>996739</t>
+          <t>996081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1846447</t>
+          <t>1806787</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2988518</t>
+          <t>2987947</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3131369</t>
+          <t>3137915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2300195</t>
+          <t>2335021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3048024</t>
+          <t>3046649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5259236</t>
+          <t>5298896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6108944</t>
+          <t>6109602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>199001</t>
+          <t>197578</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>250692</t>
+          <t>248121</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>316617</t>
+          <t>314268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>382927</t>
+          <t>379404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>530000</t>
+          <t>529353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>614085</t>
+          <t>620064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>781031</t>
+          <t>783602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>832722</t>
+          <t>834145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>932186</t>
+          <t>935709</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>998496</t>
+          <t>1000845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1732750</t>
+          <t>1726771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1816835</t>
+          <t>1817482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>527451</t>
+          <t>523500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>605538</t>
+          <t>603562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>598865</t>
+          <t>602656</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>679650</t>
+          <t>678817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1153496</t>
+          <t>1150086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1258175</t>
+          <t>1262413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1087875</t>
+          <t>1089851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1165962</t>
+          <t>1169913</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>908023</t>
+          <t>908856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>988808</t>
+          <t>985017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2022911</t>
+          <t>2018673</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2127590</t>
+          <t>2131000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144627</t>
+          <t>143870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188324</t>
+          <t>190144</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157496</t>
+          <t>158212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>200591</t>
+          <t>199108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>314220</t>
+          <t>313757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>376466</t>
+          <t>375414</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>363084</t>
+          <t>361264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406781</t>
+          <t>407538</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275821</t>
+          <t>277304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318916</t>
+          <t>318200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>651354</t>
+          <t>652406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>713600</t>
+          <t>714063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>902370</t>
+          <t>907289</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1007998</t>
+          <t>1008885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1112673</t>
+          <t>1109829</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1224850</t>
+          <t>1221313</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2052399</t>
+          <t>2046214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2205057</t>
+          <t>2200666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2268545</t>
+          <t>2267658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2374173</t>
+          <t>2369254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2154347</t>
+          <t>2157884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2266524</t>
+          <t>2269368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4450684</t>
+          <t>4455075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4603342</t>
+          <t>4609527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>354101</t>
+          <t>355971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>416326</t>
+          <t>418501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>540498</t>
+          <t>540949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>615255</t>
+          <t>615919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>918371</t>
+          <t>918445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1019677</t>
+          <t>1013027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>558317</t>
+          <t>556142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>620542</t>
+          <t>618672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>722542</t>
+          <t>721878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>797299</t>
+          <t>796848</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1292763</t>
+          <t>1299413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1394069</t>
+          <t>1393995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>901906</t>
+          <t>899479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>990419</t>
+          <t>990102</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>979400</t>
+          <t>973783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1065501</t>
+          <t>1060107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1907119</t>
+          <t>1906649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2035298</t>
+          <t>2028879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>973538</t>
+          <t>973855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1062051</t>
+          <t>1064478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>692302</t>
+          <t>697696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>778403</t>
+          <t>784020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1686462</t>
+          <t>1692881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1814641</t>
+          <t>1815111</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,77%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173084</t>
+          <t>173156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>218433</t>
+          <t>218900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>213919</t>
+          <t>211814</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>257928</t>
+          <t>257669</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>396623</t>
+          <t>396194</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>463409</t>
+          <t>466770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>262748</t>
+          <t>262281</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308097</t>
+          <t>308025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>200703</t>
+          <t>200962</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244712</t>
+          <t>246817</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>476404</t>
+          <t>473043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543190</t>
+          <t>543619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1471706</t>
+          <t>1472550</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1590298</t>
+          <t>1593706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1766895</t>
+          <t>1772792</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1889323</t>
+          <t>1896297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3272612</t>
+          <t>3277571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3446041</t>
+          <t>3449689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1829484</t>
+          <t>1826076</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1948076</t>
+          <t>1947232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1664907</t>
+          <t>1657933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1787335</t>
+          <t>1781438</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3527971</t>
+          <t>3524323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3701400</t>
+          <t>3696441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>187175</t>
+          <t>184416</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>234468</t>
+          <t>233363</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>306511</t>
+          <t>305478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>369351</t>
+          <t>367423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>508664</t>
+          <t>500680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>587789</t>
+          <t>584680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>519879</t>
+          <t>520984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>567172</t>
+          <t>569931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>625309</t>
+          <t>627237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>688149</t>
+          <t>689182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1161218</t>
+          <t>1164327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1240343</t>
+          <t>1248327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>640077</t>
+          <t>635546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>722617</t>
+          <t>723189</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>770649</t>
+          <t>770486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>854981</t>
+          <t>857112</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1424440</t>
+          <t>1426246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1556375</t>
+          <t>1554209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1353768</t>
+          <t>1353196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1436308</t>
+          <t>1440839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1133319</t>
+          <t>1131188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1217651</t>
+          <t>1217814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2508310</t>
+          <t>2510476</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2640245</t>
+          <t>2638439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>148610</t>
+          <t>146023</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192795</t>
+          <t>190846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200332</t>
+          <t>199886</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>247330</t>
+          <t>247392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>356025</t>
+          <t>358090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>425595</t>
+          <t>423185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>354091</t>
+          <t>356040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>398276</t>
+          <t>400863</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301810</t>
+          <t>301748</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>348808</t>
+          <t>349254</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>670432</t>
+          <t>672842</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>740002</t>
+          <t>737937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,33%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1000723</t>
+          <t>1004427</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1113981</t>
+          <t>1112384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1311616</t>
+          <t>1314759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1435478</t>
+          <t>1437795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2346461</t>
+          <t>2356845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2509717</t>
+          <t>2510519</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2263637</t>
+          <t>2265234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2376895</t>
+          <t>2373191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2096622</t>
+          <t>2094305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2220484</t>
+          <t>2217341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4400001</t>
+          <t>4399199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4563257</t>
+          <t>4552873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90034</t>
+          <t>99437</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75401</t>
+          <t>85744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105832</t>
+          <t>116510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>196162</t>
+          <t>218637</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178755</t>
+          <t>200354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>215870</t>
+          <t>241058</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>286196</t>
+          <t>318074</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>265133</t>
+          <t>293186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>312765</t>
+          <t>342291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>424904</t>
+          <t>479092</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409106</t>
+          <t>462019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>439537</t>
+          <t>492785</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>559346</t>
+          <t>603401</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>539638</t>
+          <t>580980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>576753</t>
+          <t>621684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>984250</t>
+          <t>1082493</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>957681</t>
+          <t>1058276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1005313</t>
+          <t>1107381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>254803</t>
+          <t>301773</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>171996</t>
+          <t>265890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>299532</t>
+          <t>341014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>523245</t>
+          <t>368474</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>338104</t>
+          <t>338035</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>948365</t>
+          <t>405213</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>778048</t>
+          <t>670247</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>568671</t>
+          <t>626072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1388735</t>
+          <t>721904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2035524</t>
+          <t>1928793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1990795</t>
+          <t>1889552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2118331</t>
+          <t>1964676</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1714578</t>
+          <t>1802918</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1289458</t>
+          <t>1766179</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1899719</t>
+          <t>1833357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3750102</t>
+          <t>3731712</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3139415</t>
+          <t>3680055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3959479</t>
+          <t>3775887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>67394</t>
+          <t>76797</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51391</t>
+          <t>59241</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88319</t>
+          <t>98484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73295</t>
+          <t>85974</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61398</t>
+          <t>70131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87154</t>
+          <t>101473</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>140689</t>
+          <t>162771</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119173</t>
+          <t>138898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165568</t>
+          <t>190800</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>579229</t>
+          <t>634790</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558304</t>
+          <t>613103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>595232</t>
+          <t>652346</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>587168</t>
+          <t>648903</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>573309</t>
+          <t>633404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>599065</t>
+          <t>664746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1166397</t>
+          <t>1283693</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1141518</t>
+          <t>1255664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1187913</t>
+          <t>1307566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>412231</t>
+          <t>478007</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>313974</t>
+          <t>433346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>463942</t>
+          <t>524533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>792702</t>
+          <t>673085</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>607145</t>
+          <t>631731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1318773</t>
+          <t>717387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1204933</t>
+          <t>1151093</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>996081</t>
+          <t>1091798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1806787</t>
+          <t>1209072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3039658</t>
+          <t>3042676</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2987947</t>
+          <t>2996150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3137915</t>
+          <t>3087337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2861092</t>
+          <t>3055222</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2335021</t>
+          <t>3010920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3046649</t>
+          <t>3096576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5900750</t>
+          <t>6097897</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5298896</t>
+          <t>6039918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6109602</t>
+          <t>6157192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
